--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126944100</v>
+        <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716477</v>
+        <v>716520</v>
       </c>
       <c r="R17" t="n">
-        <v>6376718</v>
+        <v>6376697</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126944111</v>
+        <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716520</v>
+        <v>716477</v>
       </c>
       <c r="R18" t="n">
-        <v>6376697</v>
+        <v>6376718</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98397</v>
+        <v>98472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944617</v>
+        <v>126944130</v>
       </c>
       <c r="B9" t="n">
-        <v>58374</v>
+        <v>109266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,46 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716453</v>
+        <v>716454</v>
       </c>
       <c r="R9" t="n">
-        <v>6376634</v>
+        <v>6376684</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,6 +1557,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1573,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944130</v>
+        <v>126944617</v>
       </c>
       <c r="B10" t="n">
-        <v>109260</v>
+        <v>58374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,46 +1589,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716454</v>
+        <v>716453</v>
       </c>
       <c r="R10" t="n">
-        <v>6376684</v>
+        <v>6376634</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,11 +1668,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126944118</v>
+        <v>126944092</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>105477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,26 +1922,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716486</v>
+        <v>716443</v>
       </c>
       <c r="R13" t="n">
-        <v>6376686</v>
+        <v>6376726</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126944092</v>
+        <v>126944118</v>
       </c>
       <c r="B14" t="n">
-        <v>105471</v>
+        <v>98465</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,26 +2033,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716443</v>
+        <v>716486</v>
       </c>
       <c r="R14" t="n">
-        <v>6376726</v>
+        <v>6376686</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98472</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126944090</v>
+        <v>126944109</v>
       </c>
       <c r="B3" t="n">
-        <v>105477</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>223621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716440</v>
+        <v>716520</v>
       </c>
       <c r="R3" t="n">
-        <v>6376735</v>
+        <v>6376697</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126944109</v>
+        <v>126944090</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>105477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716520</v>
+        <v>716440</v>
       </c>
       <c r="R4" t="n">
-        <v>6376697</v>
+        <v>6376735</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944130</v>
+        <v>126944617</v>
       </c>
       <c r="B9" t="n">
-        <v>109266</v>
+        <v>58374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,46 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716454</v>
+        <v>716453</v>
       </c>
       <c r="R9" t="n">
-        <v>6376684</v>
+        <v>6376634</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,11 +1557,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944617</v>
+        <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>58374</v>
+        <v>109266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,46 +1584,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716453</v>
+        <v>716454</v>
       </c>
       <c r="R10" t="n">
-        <v>6376634</v>
+        <v>6376684</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,6 +1663,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1911,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126944092</v>
+        <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>105477</v>
+        <v>98465</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,26 +1922,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716443</v>
+        <v>716486</v>
       </c>
       <c r="R13" t="n">
-        <v>6376726</v>
+        <v>6376686</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126944118</v>
+        <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>98465</v>
+        <v>105477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,26 +2033,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716486</v>
+        <v>716443</v>
       </c>
       <c r="R14" t="n">
-        <v>6376686</v>
+        <v>6376726</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126944109</v>
+        <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>105477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716520</v>
+        <v>716440</v>
       </c>
       <c r="R3" t="n">
-        <v>6376697</v>
+        <v>6376735</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126944090</v>
+        <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>105477</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>223621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716440</v>
+        <v>716520</v>
       </c>
       <c r="R4" t="n">
-        <v>6376735</v>
+        <v>6376697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B21" t="n">
-        <v>98465</v>
+        <v>98479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R21" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R22" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107324</v>
+        <v>107325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98479</v>
+        <v>98466</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R21" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98466</v>
+        <v>98479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R22" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126944090</v>
+        <v>126944109</v>
       </c>
       <c r="B3" t="n">
-        <v>105478</v>
+        <v>98479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>223621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716440</v>
+        <v>716520</v>
       </c>
       <c r="R3" t="n">
-        <v>6376735</v>
+        <v>6376697</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126944109</v>
+        <v>126944090</v>
       </c>
       <c r="B4" t="n">
-        <v>98479</v>
+        <v>105478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716520</v>
+        <v>716440</v>
       </c>
       <c r="R4" t="n">
-        <v>6376697</v>
+        <v>6376735</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944109</v>
       </c>
       <c r="B3" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944090</v>
       </c>
       <c r="B4" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944617</v>
+        <v>126944130</v>
       </c>
       <c r="B9" t="n">
-        <v>58374</v>
+        <v>109273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,46 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716453</v>
+        <v>716454</v>
       </c>
       <c r="R9" t="n">
-        <v>6376634</v>
+        <v>6376684</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,6 +1557,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1573,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944130</v>
+        <v>126944617</v>
       </c>
       <c r="B10" t="n">
-        <v>109267</v>
+        <v>58378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,46 +1589,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716454</v>
+        <v>716453</v>
       </c>
       <c r="R10" t="n">
-        <v>6376684</v>
+        <v>6376634</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,11 +1668,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126944118</v>
+        <v>126944092</v>
       </c>
       <c r="B13" t="n">
-        <v>98466</v>
+        <v>105484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,26 +1922,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716486</v>
+        <v>716443</v>
       </c>
       <c r="R13" t="n">
-        <v>6376686</v>
+        <v>6376726</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126944092</v>
+        <v>126944118</v>
       </c>
       <c r="B14" t="n">
-        <v>105478</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,26 +2033,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716443</v>
+        <v>716486</v>
       </c>
       <c r="R14" t="n">
-        <v>6376726</v>
+        <v>6376686</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98479</v>
+        <v>98483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944130</v>
+        <v>126944617</v>
       </c>
       <c r="B9" t="n">
-        <v>109273</v>
+        <v>58378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,46 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716454</v>
+        <v>716453</v>
       </c>
       <c r="R9" t="n">
-        <v>6376684</v>
+        <v>6376634</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,11 +1557,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1578,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944617</v>
+        <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>58378</v>
+        <v>109273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,46 +1584,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716453</v>
+        <v>716454</v>
       </c>
       <c r="R10" t="n">
-        <v>6376634</v>
+        <v>6376684</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,6 +1663,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944617</v>
+        <v>126944130</v>
       </c>
       <c r="B9" t="n">
-        <v>58378</v>
+        <v>109273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,46 +1478,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716453</v>
+        <v>716454</v>
       </c>
       <c r="R9" t="n">
-        <v>6376634</v>
+        <v>6376684</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,6 +1557,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1573,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944130</v>
+        <v>126944617</v>
       </c>
       <c r="B10" t="n">
-        <v>109273</v>
+        <v>58378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,46 +1589,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716454</v>
+        <v>716453</v>
       </c>
       <c r="R10" t="n">
-        <v>6376684</v>
+        <v>6376634</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,11 +1668,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1911,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126944092</v>
+        <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>105484</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,26 +1922,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716443</v>
+        <v>716486</v>
       </c>
       <c r="R13" t="n">
-        <v>6376726</v>
+        <v>6376686</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126944118</v>
+        <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>105484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,26 +2033,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716486</v>
+        <v>716443</v>
       </c>
       <c r="R14" t="n">
-        <v>6376686</v>
+        <v>6376726</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944109</v>
       </c>
       <c r="B3" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944090</v>
       </c>
       <c r="B4" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107331</v>
+        <v>107333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B21" t="n">
-        <v>98471</v>
+        <v>98484</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R21" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B22" t="n">
-        <v>98484</v>
+        <v>98471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R22" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126944109</v>
+        <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>98484</v>
+        <v>105488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223621</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716520</v>
+        <v>716440</v>
       </c>
       <c r="R3" t="n">
-        <v>6376697</v>
+        <v>6376735</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126944090</v>
+        <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>105486</v>
+        <v>98486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,26 +918,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>223621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716440</v>
+        <v>716520</v>
       </c>
       <c r="R4" t="n">
-        <v>6376735</v>
+        <v>6376697</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98484</v>
+        <v>98486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>126944617</v>
       </c>
       <c r="B9" t="n">
-        <v>58378</v>
+        <v>58380</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98484</v>
+        <v>98473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R21" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98471</v>
+        <v>98486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R22" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107333</v>
+        <v>107335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B21" t="n">
-        <v>98473</v>
+        <v>98486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R21" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B22" t="n">
-        <v>98486</v>
+        <v>98473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R22" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944088</v>
+        <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98486</v>
+        <v>98473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,21 +2825,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716437</v>
+        <v>716464</v>
       </c>
       <c r="R21" t="n">
-        <v>6376669</v>
+        <v>6376670</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944126</v>
+        <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98473</v>
+        <v>98486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>223621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716464</v>
+        <v>716437</v>
       </c>
       <c r="R22" t="n">
-        <v>6376670</v>
+        <v>6376669</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107352</v>
+        <v>107353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126944090</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>126944109</v>
       </c>
       <c r="B4" t="n">
-        <v>98486</v>
+        <v>98472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126944096</v>
       </c>
       <c r="B5" t="n">
-        <v>98486</v>
+        <v>98472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>126944124</v>
       </c>
       <c r="B6" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126944119</v>
       </c>
       <c r="B7" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>126944098</v>
       </c>
       <c r="B8" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>126944617</v>
       </c>
       <c r="B9" t="n">
-        <v>58380</v>
+        <v>58374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>126944130</v>
       </c>
       <c r="B10" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>126944122</v>
       </c>
       <c r="B11" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>126944113</v>
       </c>
       <c r="B12" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>126944118</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>126944092</v>
       </c>
       <c r="B14" t="n">
-        <v>105488</v>
+        <v>105471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>126944127</v>
       </c>
       <c r="B15" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>126944129</v>
       </c>
       <c r="B16" t="n">
-        <v>98473</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>126944111</v>
       </c>
       <c r="B17" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>126944100</v>
       </c>
       <c r="B18" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>126944089</v>
       </c>
       <c r="B19" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>126944115</v>
       </c>
       <c r="B20" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126944126</v>
       </c>
       <c r="B21" t="n">
-        <v>98473</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>126944088</v>
       </c>
       <c r="B22" t="n">
-        <v>98486</v>
+        <v>98472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127174265</v>
       </c>
       <c r="B23" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>127174261</v>
       </c>
       <c r="B24" t="n">
-        <v>107353</v>
+        <v>107318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>127174260</v>
       </c>
       <c r="B25" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127174264</v>
       </c>
       <c r="B26" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>127174267</v>
       </c>
       <c r="B27" t="n">
-        <v>105506</v>
+        <v>105471</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72871067</v>
+        <v>69378436</v>
       </c>
       <c r="B2" t="n">
-        <v>96319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219799</v>
+        <v>981</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Vit sminkrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Buglossoides arvensis var. arvensis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gardese, Gtl</t>
+          <t>Ganthem, Gardese 1:20 110 m SSO, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716540.7726182137</v>
+        <v>716394</v>
       </c>
       <c r="R2" t="n">
-        <v>6376669.574365586</v>
+        <v>6376784</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,34 +762,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Åkerhörn.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126944090</v>
+        <v>126944618</v>
       </c>
       <c r="B3" t="n">
-        <v>105488</v>
+        <v>58286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,46 +793,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716440</v>
+        <v>716483</v>
       </c>
       <c r="R3" t="n">
-        <v>6376735</v>
+        <v>6376615</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,11 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,57 +888,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126944109</v>
+        <v>126944617</v>
       </c>
       <c r="B4" t="n">
-        <v>98486</v>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223621</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Hartviks 1:40., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716520</v>
+        <v>716453</v>
       </c>
       <c r="R4" t="n">
-        <v>6376697</v>
+        <v>6376634</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,11 +978,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1018,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126944096</v>
+        <v>72871067</v>
       </c>
       <c r="B5" t="n">
-        <v>98486</v>
+        <v>99103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,43 +1005,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223621</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (4), Gtl</t>
+          <t>Gardese, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716481</v>
+        <v>716541</v>
       </c>
       <c r="R5" t="n">
-        <v>6376715</v>
+        <v>6376670</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,12 +1059,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2018-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,62 +1076,66 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126944124</v>
+        <v>126944105</v>
       </c>
       <c r="B6" t="n">
-        <v>109277</v>
+        <v>99120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,13 +1144,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716464</v>
+        <v>716511</v>
       </c>
       <c r="R6" t="n">
-        <v>6376670</v>
+        <v>6376715</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1193,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kallbarrskog.</t>
+          <t>Vägkant fuktig mot kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1240,57 +1211,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126944119</v>
+        <v>126944103</v>
       </c>
       <c r="B7" t="n">
-        <v>109277</v>
+        <v>99142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716486</v>
+        <v>716511</v>
       </c>
       <c r="R7" t="n">
-        <v>6376686</v>
+        <v>6376715</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1295,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kallbarrskog.</t>
+          <t>Vägkant fuktig mot kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1351,37 +1313,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126944098</v>
+        <v>126944118</v>
       </c>
       <c r="B8" t="n">
-        <v>109277</v>
+        <v>99142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1395,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716481</v>
+        <v>716486</v>
       </c>
       <c r="R8" t="n">
-        <v>6376715</v>
+        <v>6376686</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126944617</v>
+        <v>126944126</v>
       </c>
       <c r="B9" t="n">
-        <v>58380</v>
+        <v>99142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,24 +1457,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hartviks 1:40., Gtl</t>
+          <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716453</v>
+        <v>716464</v>
       </c>
       <c r="R9" t="n">
-        <v>6376634</v>
+        <v>6376670</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,6 +1514,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1573,37 +1535,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126944130</v>
+        <v>126944129</v>
       </c>
       <c r="B10" t="n">
-        <v>109277</v>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1617,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716454</v>
+        <v>716459</v>
       </c>
       <c r="R10" t="n">
-        <v>6376684</v>
+        <v>6376671</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1684,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126944122</v>
+        <v>127174261</v>
       </c>
       <c r="B11" t="n">
-        <v>109277</v>
+        <v>108116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,31 +1657,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1728,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716470</v>
+        <v>716418</v>
       </c>
       <c r="R11" t="n">
-        <v>6376680</v>
+        <v>6376756</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1795,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126944113</v>
+        <v>126944089</v>
       </c>
       <c r="B12" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1787,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1839,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716503</v>
+        <v>716440</v>
       </c>
       <c r="R12" t="n">
-        <v>6376699</v>
+        <v>6376735</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1875,11 +1837,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,37 +1868,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126944118</v>
+        <v>126944098</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>110078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1955,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716486</v>
+        <v>716481</v>
       </c>
       <c r="R13" t="n">
-        <v>6376686</v>
+        <v>6376715</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1991,6 +1948,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,37 +1984,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126944092</v>
+        <v>126944100</v>
       </c>
       <c r="B14" t="n">
-        <v>105488</v>
+        <v>110078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2066,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716443</v>
+        <v>716477</v>
       </c>
       <c r="R14" t="n">
-        <v>6376726</v>
+        <v>6376718</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2102,6 +2064,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126944127</v>
+        <v>126944107</v>
       </c>
       <c r="B15" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,29 +2128,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716459</v>
+        <v>716511</v>
       </c>
       <c r="R15" t="n">
-        <v>6376671</v>
+        <v>6376715</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,6 +2173,11 @@
           <t>2025-06-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2226,7 +2189,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kallbarrskog.</t>
+          <t>Vägkant fuktig mot kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2244,37 +2207,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126944129</v>
+        <v>126944111</v>
       </c>
       <c r="B16" t="n">
-        <v>98473</v>
+        <v>110078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2288,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716459</v>
+        <v>716520</v>
       </c>
       <c r="R16" t="n">
-        <v>6376671</v>
+        <v>6376697</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2324,6 +2287,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2323,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126944111</v>
+        <v>126944113</v>
       </c>
       <c r="B17" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716520</v>
+        <v>716503</v>
       </c>
       <c r="R17" t="n">
-        <v>6376697</v>
+        <v>6376699</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,10 +2439,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126944100</v>
+        <v>126944115</v>
       </c>
       <c r="B18" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2469,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2515,10 +2483,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716477</v>
+        <v>716490</v>
       </c>
       <c r="R18" t="n">
-        <v>6376718</v>
+        <v>6376693</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2587,10 +2555,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126944089</v>
+        <v>126944119</v>
       </c>
       <c r="B19" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2585,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716440</v>
+        <v>716486</v>
       </c>
       <c r="R19" t="n">
-        <v>6376735</v>
+        <v>6376686</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2698,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126944115</v>
+        <v>126944122</v>
       </c>
       <c r="B20" t="n">
-        <v>109277</v>
+        <v>110078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2728,12 +2696,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2742,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716490</v>
+        <v>716470</v>
       </c>
       <c r="R20" t="n">
-        <v>6376693</v>
+        <v>6376680</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2778,11 +2746,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2814,42 +2777,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126944126</v>
+        <v>126944124</v>
       </c>
       <c r="B21" t="n">
-        <v>98473</v>
+        <v>110078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2925,42 +2888,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126944088</v>
+        <v>126944127</v>
       </c>
       <c r="B22" t="n">
-        <v>98486</v>
+        <v>110078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>223621</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2969,10 +2932,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716437</v>
+        <v>716459</v>
       </c>
       <c r="R22" t="n">
-        <v>6376669</v>
+        <v>6376671</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3036,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127174265</v>
+        <v>126944130</v>
       </c>
       <c r="B23" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,17 +3027,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716436</v>
+        <v>716454</v>
       </c>
       <c r="R23" t="n">
-        <v>6376739</v>
+        <v>6376684</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3138,10 +3110,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127174261</v>
+        <v>127174260</v>
       </c>
       <c r="B24" t="n">
-        <v>107353</v>
+        <v>110078</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,26 +3121,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3218,6 +3190,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127174260</v>
+        <v>127174264</v>
       </c>
       <c r="B25" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,26 +3254,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (4), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716418</v>
+        <v>716421</v>
       </c>
       <c r="R25" t="n">
-        <v>6376756</v>
+        <v>6376753</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3329,11 +3297,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3365,10 +3328,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127174264</v>
+        <v>127174265</v>
       </c>
       <c r="B26" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3400,10 +3363,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716421</v>
+        <v>716436</v>
       </c>
       <c r="R26" t="n">
-        <v>6376753</v>
+        <v>6376739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3467,10 +3430,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127174267</v>
+        <v>126944090</v>
       </c>
       <c r="B27" t="n">
-        <v>105506</v>
+        <v>106244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,7 +3460,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3511,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716436</v>
+        <v>716440</v>
       </c>
       <c r="R27" t="n">
-        <v>6376739</v>
+        <v>6376735</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3575,6 +3538,672 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126944092</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>716443</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6376726</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127174267</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>716436</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6376739</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126944088</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>716437</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6376669</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126944096</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>716481</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6376715</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126944108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>716511</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6376715</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Vägkant fuktig mot kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126944109</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99155</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (4), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>716520</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6376697</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4984-2025 artfynd.xlsx
+++ b/artfynd/A 4984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69378436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871067</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944105</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944103</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944118</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944126</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944089</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944098</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2204,6 +2274,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944107</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2320,6 +2395,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944111</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2436,6 +2516,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944113</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2552,6 +2637,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944115</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2663,6 +2753,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944119</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2774,6 +2869,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944122</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2885,6 +2985,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944124</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2996,6 +3101,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944127</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3107,6 +3217,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944130</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3223,6 +3338,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174260</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3325,6 +3445,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174264</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174265</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3538,6 +3668,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944090</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3649,6 +3784,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944092</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3760,6 +3900,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174267</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3871,6 +4016,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944088</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3982,6 +4132,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944096</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4093,6 +4248,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944108</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4204,8 +4364,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126944109</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>